--- a/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,22 +9837,22 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1322.91</v>
+        <v>1218.96</v>
       </c>
       <c r="C4" t="n">
-        <v>202104</v>
+        <v>18648</v>
       </c>
       <c r="D4" t="n">
-        <v>158796</v>
+        <v>14652</v>
       </c>
       <c r="E4" t="n">
-        <v>34200</v>
+        <v>1800</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2670</v>
+        <v>4350</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -9873,7 +9867,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>6930</v>
+        <v>22320</v>
       </c>
     </row>
     <row r="5">
@@ -9881,22 +9875,22 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>2698.38</v>
+        <v>260.91</v>
       </c>
       <c r="C5" t="n">
-        <v>378504</v>
+        <v>4032</v>
       </c>
       <c r="D5" t="n">
-        <v>297396</v>
+        <v>3168</v>
       </c>
       <c r="E5" t="n">
-        <v>45900</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6090</v>
+        <v>1110</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -9911,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>10230</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="6">
@@ -9919,22 +9913,22 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3110.76</v>
+        <v>31.59</v>
       </c>
       <c r="C6" t="n">
-        <v>258048</v>
+        <v>1512</v>
       </c>
       <c r="D6" t="n">
-        <v>202752</v>
+        <v>1188</v>
       </c>
       <c r="E6" t="n">
-        <v>26100</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5730</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -9949,7 +9943,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9270</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="7">
@@ -9957,22 +9951,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2234.16</v>
+        <v>12.87</v>
       </c>
       <c r="C7" t="n">
-        <v>141120</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>110880</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4050</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -9987,7 +9981,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5760</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="8">
@@ -9995,22 +9989,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1246.86</v>
+        <v>17.1</v>
       </c>
       <c r="C8" t="n">
-        <v>52920</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>41580</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1410</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -10025,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3360</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="9">
@@ -10033,22 +10027,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>614.0700000000001</v>
+        <v>11.34</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>13860</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>840</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10063,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>510</v>
+        <v>930</v>
       </c>
     </row>
     <row r="10">
@@ -10071,13 +10065,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>380.79</v>
+        <v>1.26</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10086,7 +10080,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -10109,13 +10103,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.19</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10124,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -10147,13 +10141,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.96</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10162,7 +10156,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -10185,7 +10179,7 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.57</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -10223,13 +10217,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -10238,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -10261,7 +10255,7 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -10299,7 +10293,7 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -10337,7 +10331,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -10375,7 +10369,7 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10413,7 +10407,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,19 +11739,19 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1214.27</v>
+        <v>117.41</v>
       </c>
       <c r="C5" t="n">
-        <v>208177.2</v>
+        <v>2217.6</v>
       </c>
       <c r="D5" t="n">
-        <v>98438.08</v>
+        <v>1048.61</v>
       </c>
       <c r="E5" t="n">
-        <v>5062.77</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -11775,7 +11769,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2148.3</v>
+        <v>1562.4</v>
       </c>
     </row>
     <row r="6">
@@ -11783,22 +11777,22 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2488.61</v>
+        <v>25.27</v>
       </c>
       <c r="C6" t="n">
-        <v>232243.2</v>
+        <v>1360.8</v>
       </c>
       <c r="D6" t="n">
-        <v>102795.26</v>
+        <v>602.3200000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>4410.9</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>286.5</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -11813,7 +11807,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3429.9</v>
+        <v>1343.1</v>
       </c>
     </row>
     <row r="7">
@@ -11821,22 +11815,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2122.45</v>
+        <v>12.23</v>
       </c>
       <c r="C7" t="n">
-        <v>141120</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>70741.44</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1531.44</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>607.5</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -11851,7 +11845,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3456</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="8">
@@ -11859,22 +11853,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1246.86</v>
+        <v>17.1</v>
       </c>
       <c r="C8" t="n">
-        <v>52920</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>30602.88</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1324.62</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>916.5</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -11889,7 +11883,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2385.6</v>
+        <v>1192.8</v>
       </c>
     </row>
     <row r="9">
@@ -11897,22 +11891,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>614.0700000000001</v>
+        <v>11.34</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>11129.58</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11927,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>413.1</v>
+        <v>753.3</v>
       </c>
     </row>
     <row r="10">
@@ -11935,13 +11929,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>380.79</v>
+        <v>1.26</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -11950,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>400.5</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="11">
@@ -11973,13 +11967,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.19</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2134.84</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11988,7 +11982,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -12011,13 +12005,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>156.96</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>734.1799999999999</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12026,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -12049,7 +12043,7 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.57</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -12087,13 +12081,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12102,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -12125,7 +12119,7 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -12163,7 +12157,7 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -12201,7 +12195,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -12239,7 +12233,7 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -12277,7 +12271,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,19 +12671,19 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>2671396.2</v>
+        <v>258300.9</v>
       </c>
       <c r="C5" t="n">
-        <v>11449746</v>
+        <v>121968</v>
       </c>
       <c r="D5" t="n">
-        <v>9974730.24</v>
+        <v>106255.45</v>
       </c>
       <c r="E5" t="n">
-        <v>932764.74</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2500.02</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -12707,7 +12701,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20236.99</v>
+        <v>14717.81</v>
       </c>
     </row>
     <row r="6">
@@ -12715,22 +12709,22 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>5474937.6</v>
+        <v>55598.4</v>
       </c>
       <c r="C6" t="n">
-        <v>12773376</v>
+        <v>74844</v>
       </c>
       <c r="D6" t="n">
-        <v>10416244.1</v>
+        <v>61032.68</v>
       </c>
       <c r="E6" t="n">
-        <v>812664.22</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>12500.1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5300.25</v>
+        <v>27.75</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -12745,7 +12739,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>32309.66</v>
+        <v>12652</v>
       </c>
     </row>
     <row r="7">
@@ -12753,22 +12747,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>4669394.4</v>
+        <v>26898.3</v>
       </c>
       <c r="C7" t="n">
-        <v>7761600</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>7168230.12</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>282152.51</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>11238.75</v>
+        <v>83.25</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -12783,7 +12777,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>32555.52</v>
+        <v>11699.64</v>
       </c>
     </row>
     <row r="8">
@@ -12791,22 +12785,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2743092</v>
+        <v>37620</v>
       </c>
       <c r="C8" t="n">
-        <v>2910600</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>3100989.83</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>244047.99</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>16955.25</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12821,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>22472.35</v>
+        <v>11236.18</v>
       </c>
     </row>
     <row r="9">
@@ -12829,22 +12823,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1350954</v>
+        <v>24948</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13209</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12859,7 +12853,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3891.4</v>
+        <v>7096.09</v>
       </c>
     </row>
     <row r="10">
@@ -12867,13 +12861,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>837738</v>
+        <v>2772</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12882,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7215</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3772.71</v>
+        <v>1257.57</v>
       </c>
     </row>
     <row r="11">
@@ -12905,13 +12899,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>473418</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>166320</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>216322.93</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12920,7 +12914,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -12943,13 +12937,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>345312</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>55440</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>74394.86</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12958,7 +12952,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>847.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -12981,7 +12975,7 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>370854</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2775</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13019,13 +13013,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>94248</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13034,7 +13028,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7770</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13057,7 +13051,7 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>9504</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -13095,7 +13089,7 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -13133,7 +13127,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -13171,7 +13165,7 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -13209,7 +13203,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,22 +13565,22 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1218.96</v>
+        <v>4.68</v>
       </c>
       <c r="C4" t="n">
-        <v>18648</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>14652</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4350</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -13601,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>22320</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
@@ -13609,13 +13603,13 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>260.91</v>
+        <v>0.09</v>
       </c>
       <c r="C5" t="n">
-        <v>4032</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>3168</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -13624,7 +13618,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1110</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -13639,7 +13633,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7440</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13647,13 +13641,13 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>31.59</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -13662,7 +13656,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -13677,7 +13671,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3630</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13685,7 +13679,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>12.87</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -13700,7 +13694,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -13715,7 +13709,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2070</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -13723,7 +13717,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -13753,7 +13747,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -13761,7 +13755,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>11.34</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -13776,7 +13770,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -13791,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -13799,7 +13793,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,13 +14535,13 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>117.41</v>
+        <v>0.04</v>
       </c>
       <c r="C5" t="n">
-        <v>2217.6</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1048.61</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -14571,7 +14565,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1562.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14579,13 +14573,13 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>25.27</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1360.8</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>602.3200000000001</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -14594,7 +14588,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -14609,7 +14603,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1343.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14617,7 +14611,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>12.23</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -14632,7 +14626,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -14647,7 +14641,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -14655,7 +14649,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -14685,7 +14679,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1192.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -14693,7 +14687,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>11.34</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -14708,7 +14702,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14723,7 +14717,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>753.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -14731,7 +14725,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>133.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,4667 +15467,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>258300.9</v>
-      </c>
-      <c r="C5" t="n">
-        <v>121968</v>
-      </c>
-      <c r="D5" t="n">
-        <v>106255.45</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14717.81</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>55598.4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>74844</v>
-      </c>
-      <c r="D6" t="n">
-        <v>61032.68</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>12652</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>26898.3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>83.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>11699.64</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>37620</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>11236.18</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>24948</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7096.09</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2772</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1257.57</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1800.72</v>
-      </c>
-      <c r="C4" t="n">
-        <v>165312</v>
-      </c>
-      <c r="D4" t="n">
-        <v>129888</v>
-      </c>
-      <c r="E4" t="n">
-        <v>29700</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1110</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2490</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3708.54</v>
-      </c>
-      <c r="C5" t="n">
-        <v>303912</v>
-      </c>
-      <c r="D5" t="n">
-        <v>238788</v>
-      </c>
-      <c r="E5" t="n">
-        <v>57600</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6450</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4216.77</v>
-      </c>
-      <c r="C6" t="n">
-        <v>237888</v>
-      </c>
-      <c r="D6" t="n">
-        <v>186912</v>
-      </c>
-      <c r="E6" t="n">
-        <v>44100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3930</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7890</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3407.49</v>
-      </c>
-      <c r="C7" t="n">
-        <v>160776</v>
-      </c>
-      <c r="D7" t="n">
-        <v>126324</v>
-      </c>
-      <c r="E7" t="n">
-        <v>17100</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3180</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>10440</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2473.65</v>
-      </c>
-      <c r="C8" t="n">
-        <v>56952</v>
-      </c>
-      <c r="D8" t="n">
-        <v>44748</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2070</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4320</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1693.17</v>
-      </c>
-      <c r="C9" t="n">
-        <v>28224</v>
-      </c>
-      <c r="D9" t="n">
-        <v>22176</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>330</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>884.4299999999999</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4356</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>210</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>527.3099999999999</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>397.44</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>367.11</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.31</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>792</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>244.08</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1668.84</v>
-      </c>
-      <c r="C5" t="n">
-        <v>167151.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>79038.83</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6353.28</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1354.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3373.42</v>
-      </c>
-      <c r="C6" t="n">
-        <v>214099.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>94764.38</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7452.9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>196.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2919.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3237.12</v>
-      </c>
-      <c r="C7" t="n">
-        <v>160776</v>
-      </c>
-      <c r="D7" t="n">
-        <v>80594.71000000001</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3637.17</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>477</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6264</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2473.65</v>
-      </c>
-      <c r="C8" t="n">
-        <v>56952</v>
-      </c>
-      <c r="D8" t="n">
-        <v>32934.53</v>
-      </c>
-      <c r="E8" t="n">
-        <v>662.3099999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1345.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3067.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1693.17</v>
-      </c>
-      <c r="C9" t="n">
-        <v>28224</v>
-      </c>
-      <c r="D9" t="n">
-        <v>17807.33</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>280.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>631.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>884.4299999999999</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3789.72</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>210</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>186.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>527.3099999999999</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2490.64</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>397.44</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1101.28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>367.11</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1504.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.31</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>769.8200000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>244.08</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1171.37</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.84</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3671454.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>9193338</v>
-      </c>
-      <c r="D5" t="n">
-        <v>8009004.44</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1170528.31</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3333.36</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>12759.39</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7421515.2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>11775456</v>
-      </c>
-      <c r="D6" t="n">
-        <v>9602475.029999999</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1373122.3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3635.25</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>27499.81</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7121654.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8842680</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8166662.17</v>
-      </c>
-      <c r="E7" t="n">
-        <v>670112.2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8824.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>59006.88</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5442030</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3132360</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3337255.72</v>
-      </c>
-      <c r="E8" t="n">
-        <v>122023.99</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>24891.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>28893.02</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3724974</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1552320</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1804416.55</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5189.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5951.56</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1945746</v>
-      </c>
-      <c r="C10" t="n">
-        <v>304920</v>
-      </c>
-      <c r="D10" t="n">
-        <v>384012.33</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1760.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1160082</v>
-      </c>
-      <c r="C11" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D11" t="n">
-        <v>252376.75</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>874368</v>
-      </c>
-      <c r="C12" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D12" t="n">
-        <v>111592.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>807642</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1080882</v>
-      </c>
-      <c r="C14" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78006.27</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>536976</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>94248</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>59400</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.04</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
@@ -538,7 +538,7 @@
         <v>1470</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -576,7 +576,7 @@
         <v>1830</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1508,7 +1508,7 @@
         <v>1830</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>658.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>182257.02</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>658.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>0.3</v>
@@ -16420,7 +16420,7 @@
         <v>182257.02</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>17499.9</v>
@@ -17314,7 +17314,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>

--- a/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
@@ -544,7 +544,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L4" t="n">
         <v>89370</v>
@@ -582,7 +582,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="L5" t="n">
         <v>84570</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
         <v>58110</v>
@@ -658,7 +658,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L7" t="n">
         <v>33960</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>14430</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>3870</v>
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L4" t="n">
         <v>34050</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L5" t="n">
         <v>32070</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
         <v>20700</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>8460</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>930</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>9.66</v>
       </c>
       <c r="L5" t="n">
         <v>6734.7</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="L6" t="n">
         <v>7659</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="L7" t="n">
         <v>5076</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>753.3</v>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>206086.44</v>
       </c>
       <c r="L5" t="n">
         <v>63440.87</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>152538.1</v>
       </c>
       <c r="L6" t="n">
         <v>72147.78</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>52481.64</v>
       </c>
       <c r="L7" t="n">
         <v>47815.92</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L9" t="n">
         <v>7096.09</v>
@@ -9902,7 +9902,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>7440</v>
@@ -10834,7 +10834,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>22.26</v>
       </c>
       <c r="L5" t="n">
         <v>17759.7</v>
@@ -10872,7 +10872,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="L6" t="n">
         <v>21500.7</v>
@@ -10910,7 +10910,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="L7" t="n">
         <v>20376</v>
@@ -10948,7 +10948,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L8" t="n">
         <v>10245.3</v>
@@ -10986,7 +10986,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>3134.7</v>
@@ -11766,7 +11766,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="L5" t="n">
         <v>1562.4</v>
@@ -12698,7 +12698,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8960.280000000001</v>
       </c>
       <c r="L5" t="n">
         <v>14717.81</v>
@@ -16426,7 +16426,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>474894.84</v>
       </c>
       <c r="L5" t="n">
         <v>167296.37</v>
@@ -16464,7 +16464,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>249607.8</v>
       </c>
       <c r="L6" t="n">
         <v>202536.59</v>
@@ -16502,7 +16502,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>122457.16</v>
       </c>
       <c r="L7" t="n">
         <v>191941.92</v>
@@ -16540,7 +16540,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>57601.8</v>
       </c>
       <c r="L8" t="n">
         <v>96510.73</v>
@@ -16578,7 +16578,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>128004</v>
       </c>
       <c r="L9" t="n">
         <v>29528.87</v>
@@ -17320,7 +17320,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L4" t="n">
         <v>21510</v>
@@ -17358,7 +17358,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L5" t="n">
         <v>27540</v>
@@ -17396,7 +17396,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>15990</v>
@@ -17434,7 +17434,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>6840</v>
@@ -17472,7 +17472,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2160</v>
@@ -17510,7 +17510,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>720</v>
@@ -18290,7 +18290,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>11.34</v>
       </c>
       <c r="L5" t="n">
         <v>5783.4</v>
@@ -18328,7 +18328,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>5916.3</v>
@@ -18366,7 +18366,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="L7" t="n">
         <v>4104</v>
@@ -18404,7 +18404,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
         <v>1533.6</v>
@@ -18442,7 +18442,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>583.2</v>
@@ -19222,7 +19222,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>241927.56</v>
       </c>
       <c r="L5" t="n">
         <v>54479.63</v>
@@ -19260,7 +19260,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>83202.60000000001</v>
       </c>
       <c r="L6" t="n">
         <v>55731.55</v>
@@ -19298,7 +19298,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>69975.52</v>
       </c>
       <c r="L7" t="n">
         <v>38659.68</v>
@@ -19336,7 +19336,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>38401.2</v>
       </c>
       <c r="L8" t="n">
         <v>14446.51</v>
@@ -19374,7 +19374,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L9" t="n">
         <v>5493.74</v>

--- a/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>9179.370000000001</v>
+        <v>9166.23</v>
       </c>
       <c r="C4" t="n">
         <v>1423800</v>
@@ -532,7 +537,7 @@
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>31230</v>
+        <v>31260</v>
       </c>
       <c r="H4" t="n">
         <v>1470</v>
@@ -544,10 +549,13 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L4" t="n">
         <v>89370</v>
+      </c>
+      <c r="M4" t="n">
+        <v>25830</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>13408.65</v>
+        <v>13395.06</v>
       </c>
       <c r="C5" t="n">
         <v>1476720</v>
@@ -570,7 +578,7 @@
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>27720</v>
+        <v>27690</v>
       </c>
       <c r="H5" t="n">
         <v>1830</v>
@@ -582,10 +590,13 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="L5" t="n">
         <v>84570</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15330</v>
       </c>
     </row>
     <row r="6">
@@ -620,10 +631,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
         <v>58110</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5730</v>
       </c>
     </row>
     <row r="7">
@@ -663,6 +677,9 @@
       <c r="L7" t="n">
         <v>33960</v>
       </c>
+      <c r="M7" t="n">
+        <v>2730</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -701,6 +718,9 @@
       <c r="L8" t="n">
         <v>14430</v>
       </c>
+      <c r="M8" t="n">
+        <v>870</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -739,6 +759,9 @@
       <c r="L9" t="n">
         <v>3870</v>
       </c>
+      <c r="M9" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -777,6 +800,9 @@
       <c r="L10" t="n">
         <v>1740</v>
       </c>
+      <c r="M10" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -815,6 +841,9 @@
       <c r="L11" t="n">
         <v>1470</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -853,6 +882,9 @@
       <c r="L12" t="n">
         <v>330</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>240</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>540</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1464,7 +1541,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>16410</v>
+        <v>16500</v>
       </c>
       <c r="H4" t="n">
         <v>1260</v>
@@ -1479,7 +1556,10 @@
         <v>32</v>
       </c>
       <c r="L4" t="n">
-        <v>34050</v>
+        <v>34110</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6900</v>
       </c>
     </row>
     <row r="5">
@@ -1487,7 +1567,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3515.94</v>
+        <v>3515.85</v>
       </c>
       <c r="C5" t="n">
         <v>379512</v>
@@ -1517,7 +1597,10 @@
         <v>23</v>
       </c>
       <c r="L5" t="n">
-        <v>32070</v>
+        <v>32130</v>
+      </c>
+      <c r="M5" t="n">
+        <v>8580</v>
       </c>
     </row>
     <row r="6">
@@ -1557,6 +1640,9 @@
       <c r="L6" t="n">
         <v>20700</v>
       </c>
+      <c r="M6" t="n">
+        <v>3420</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1595,6 +1681,9 @@
       <c r="L7" t="n">
         <v>8460</v>
       </c>
+      <c r="M7" t="n">
+        <v>2010</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1633,6 +1722,9 @@
       <c r="L8" t="n">
         <v>2790</v>
       </c>
+      <c r="M8" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1671,6 +1763,9 @@
       <c r="L9" t="n">
         <v>930</v>
       </c>
+      <c r="M9" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1804,9 @@
       <c r="L10" t="n">
         <v>660</v>
       </c>
+      <c r="M10" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,7 +1843,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1140</v>
+        <v>1170</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1785,6 +1886,9 @@
       <c r="L12" t="n">
         <v>240</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1823,6 +1927,9 @@
       <c r="L13" t="n">
         <v>90</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1861,6 +1968,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2419,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1582.17</v>
+        <v>1582.13</v>
       </c>
       <c r="C5" t="n">
         <v>208731.6</v>
@@ -2440,16 +2592,19 @@
         <v>658.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9.66</v>
+        <v>7.61</v>
       </c>
       <c r="L5" t="n">
-        <v>6734.7</v>
+        <v>6747.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>171.6</v>
       </c>
     </row>
     <row r="6">
@@ -2484,10 +2639,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>7.15</v>
+        <v>5.58</v>
       </c>
       <c r="L6" t="n">
         <v>7659</v>
+      </c>
+      <c r="M6" t="n">
+        <v>273.6</v>
       </c>
     </row>
     <row r="7">
@@ -2522,10 +2680,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>5076</v>
+      </c>
+      <c r="M7" t="n">
+        <v>703.5</v>
       </c>
     </row>
     <row r="8">
@@ -2565,6 +2726,9 @@
       <c r="L8" t="n">
         <v>1980.9</v>
       </c>
+      <c r="M8" t="n">
+        <v>396</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2598,10 +2762,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="L9" t="n">
         <v>753.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -2641,6 +2808,9 @@
       <c r="L10" t="n">
         <v>587.4</v>
       </c>
+      <c r="M10" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2677,7 +2847,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1140</v>
+        <v>1170</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2717,6 +2890,9 @@
       <c r="L12" t="n">
         <v>240</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2755,6 +2931,9 @@
       <c r="L13" t="n">
         <v>90</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2793,6 +2972,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2831,6 +3013,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3351,16 +3575,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3480780.6</v>
+        <v>3480691.5</v>
       </c>
       <c r="C5" t="n">
-        <v>11480238</v>
+        <v>8766727.199999999</v>
       </c>
       <c r="D5" t="n">
-        <v>10001294.1</v>
+        <v>18950443.78</v>
       </c>
       <c r="E5" t="n">
-        <v>1755792.46</v>
+        <v>3287822.4</v>
       </c>
       <c r="F5" t="n">
         <v>1666.68</v>
@@ -3369,19 +3593,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>182257.02</v>
+        <v>3755160</v>
       </c>
       <c r="I5" t="n">
-        <v>57499.5</v>
+        <v>64288.14</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>206086.44</v>
+        <v>369656.83</v>
       </c>
       <c r="L5" t="n">
-        <v>63440.87</v>
+        <v>1214514</v>
+      </c>
+      <c r="M5" t="n">
+        <v>51480</v>
       </c>
     </row>
     <row r="6">
@@ -3392,22 +3619,22 @@
         <v>7046424</v>
       </c>
       <c r="C6" t="n">
-        <v>12399156</v>
+        <v>9468446.4</v>
       </c>
       <c r="D6" t="n">
-        <v>10111080.7</v>
+        <v>19158467.33</v>
       </c>
       <c r="E6" t="n">
-        <v>1793465.86</v>
+        <v>3358368</v>
       </c>
       <c r="F6" t="n">
         <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>6105</v>
+        <v>17820</v>
       </c>
       <c r="H6" t="n">
-        <v>525109.36</v>
+        <v>10819170</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3416,10 +3643,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>152538.1</v>
+        <v>270796.81</v>
       </c>
       <c r="L6" t="n">
-        <v>72147.78</v>
+        <v>1378620</v>
+      </c>
+      <c r="M6" t="n">
+        <v>82080</v>
       </c>
     </row>
     <row r="7">
@@ -3430,22 +3660,22 @@
         <v>7384429.8</v>
       </c>
       <c r="C7" t="n">
-        <v>6347880</v>
+        <v>4847472</v>
       </c>
       <c r="D7" t="n">
-        <v>5862588.2</v>
+        <v>11108427.26</v>
       </c>
       <c r="E7" t="n">
-        <v>952264.71</v>
+        <v>1783170.45</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>9990</v>
+        <v>29160</v>
       </c>
       <c r="H7" t="n">
-        <v>24234.54</v>
+        <v>499320</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3454,10 +3684,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>52481.64</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>47815.92</v>
+        <v>913680</v>
+      </c>
+      <c r="M7" t="n">
+        <v>211050</v>
       </c>
     </row>
     <row r="8">
@@ -3468,22 +3701,22 @@
         <v>4950396</v>
       </c>
       <c r="C8" t="n">
-        <v>2661120</v>
+        <v>2032128</v>
       </c>
       <c r="D8" t="n">
-        <v>2835190.7</v>
+        <v>5372116.99</v>
       </c>
       <c r="E8" t="n">
-        <v>244047.99</v>
+        <v>456993.9</v>
       </c>
       <c r="F8" t="n">
         <v>79167.3</v>
       </c>
       <c r="G8" t="n">
-        <v>55555.5</v>
+        <v>162162</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3495,7 +3728,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>18660.08</v>
+        <v>356562</v>
+      </c>
+      <c r="M8" t="n">
+        <v>118800</v>
       </c>
     </row>
     <row r="9">
@@ -3506,22 +3742,22 @@
         <v>2117016</v>
       </c>
       <c r="C9" t="n">
-        <v>720720</v>
+        <v>550368</v>
       </c>
       <c r="D9" t="n">
-        <v>837764.83</v>
+        <v>1587396.1</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13680.75</v>
+        <v>39933</v>
       </c>
       <c r="H9" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3530,10 +3766,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>64002</v>
+        <v>116971.4</v>
       </c>
       <c r="L9" t="n">
-        <v>7096.09</v>
+        <v>135594</v>
+      </c>
+      <c r="M9" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,22 +3783,22 @@
         <v>960300</v>
       </c>
       <c r="C10" t="n">
-        <v>443520</v>
+        <v>338688</v>
       </c>
       <c r="D10" t="n">
-        <v>558563.39</v>
+        <v>1058365.44</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>90045</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3571,7 +3810,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5533.31</v>
+        <v>105732</v>
+      </c>
+      <c r="M10" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,10 +3824,10 @@
         <v>643896</v>
       </c>
       <c r="C11" t="n">
-        <v>471240</v>
+        <v>359856</v>
       </c>
       <c r="D11" t="n">
-        <v>612914.97</v>
+        <v>1161350.78</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3594,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3609,7 +3851,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10738.8</v>
+        <v>210600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3620,10 +3865,10 @@
         <v>533412</v>
       </c>
       <c r="C12" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D12" t="n">
-        <v>297579.46</v>
+        <v>563853.3100000001</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -3632,10 +3877,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H12" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3647,7 +3892,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2260.8</v>
+        <v>43200</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3658,10 +3906,10 @@
         <v>626670</v>
       </c>
       <c r="C13" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D13" t="n">
-        <v>152401.13</v>
+        <v>288769.54</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -3673,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3685,7 +3933,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3696,10 +3947,10 @@
         <v>702504</v>
       </c>
       <c r="C14" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D14" t="n">
-        <v>156012.53</v>
+        <v>295612.42</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3723,6 +3974,9 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3734,10 +3988,10 @@
         <v>278982</v>
       </c>
       <c r="C15" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D15" t="n">
-        <v>79129.81</v>
+        <v>149935.1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3761,6 +4015,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3772,10 +4029,10 @@
         <v>212652</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3799,6 +4056,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3839,6 +4099,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3877,6 +4140,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3915,6 +4181,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4275,6 +4568,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4315,6 +4611,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4353,6 +4652,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5247,6 +5615,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -5285,6 +5656,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -5323,6 +5697,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6179,6 +6619,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -6217,6 +6660,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -6255,6 +6701,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -6293,6 +6742,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -6331,6 +6783,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7071,6 +7580,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7111,6 +7623,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8043,6 +8627,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -8081,6 +8668,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -8119,6 +8709,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -8157,6 +8750,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8975,6 +9631,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -9013,6 +9672,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -9051,6 +9713,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -9089,6 +9754,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9867,7 +10592,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>22320</v>
+        <v>22350</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5880</v>
       </c>
     </row>
     <row r="5">
@@ -9907,6 +10635,9 @@
       <c r="L5" t="n">
         <v>7440</v>
       </c>
+      <c r="M5" t="n">
+        <v>2910</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -9945,6 +10676,9 @@
       <c r="L6" t="n">
         <v>3630</v>
       </c>
+      <c r="M6" t="n">
+        <v>930</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -9983,6 +10717,9 @@
       <c r="L7" t="n">
         <v>2070</v>
       </c>
+      <c r="M7" t="n">
+        <v>270</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -10021,6 +10758,9 @@
       <c r="L8" t="n">
         <v>1680</v>
       </c>
+      <c r="M8" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10059,6 +10799,9 @@
       <c r="L9" t="n">
         <v>930</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>150</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>6033.89</v>
+        <v>6027.78</v>
       </c>
       <c r="C5" t="n">
         <v>812196</v>
@@ -10828,16 +11628,19 @@
         <v>658.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="J5" t="n">
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>22.26</v>
+        <v>14.9</v>
       </c>
       <c r="L5" t="n">
         <v>17759.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>306.6</v>
       </c>
     </row>
     <row r="6">
@@ -10872,10 +11675,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>11.7</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>21500.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>458.4</v>
       </c>
     </row>
     <row r="7">
@@ -10910,10 +11716,13 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5.74</v>
+        <v>4.47</v>
       </c>
       <c r="L7" t="n">
         <v>20376</v>
+      </c>
+      <c r="M7" t="n">
+        <v>955.5</v>
       </c>
     </row>
     <row r="8">
@@ -10948,10 +11757,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="L8" t="n">
         <v>10245.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>522</v>
       </c>
     </row>
     <row r="9">
@@ -10986,10 +11798,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>4.82</v>
       </c>
       <c r="L9" t="n">
         <v>3134.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="10">
@@ -11029,6 +11844,9 @@
       <c r="L10" t="n">
         <v>1548.6</v>
       </c>
+      <c r="M10" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -11067,6 +11885,9 @@
       <c r="L11" t="n">
         <v>1470</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -11105,6 +11926,9 @@
       <c r="L12" t="n">
         <v>330</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -11143,6 +11967,9 @@
       <c r="L13" t="n">
         <v>240</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -11181,6 +12008,9 @@
       <c r="L14" t="n">
         <v>540</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -11219,6 +12049,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11766,10 +12638,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="L5" t="n">
         <v>1562.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>58.2</v>
       </c>
     </row>
     <row r="6">
@@ -11809,6 +12684,9 @@
       <c r="L6" t="n">
         <v>1343.1</v>
       </c>
+      <c r="M6" t="n">
+        <v>74.40000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -11847,6 +12725,9 @@
       <c r="L7" t="n">
         <v>1242</v>
       </c>
+      <c r="M7" t="n">
+        <v>94.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -11885,6 +12766,9 @@
       <c r="L8" t="n">
         <v>1192.8</v>
       </c>
+      <c r="M8" t="n">
+        <v>54</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -11923,6 +12807,9 @@
       <c r="L9" t="n">
         <v>753.3</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -11961,6 +12848,9 @@
       <c r="L10" t="n">
         <v>133.5</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -11999,6 +12889,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,10 +13618,10 @@
         <v>258300.9</v>
       </c>
       <c r="C5" t="n">
-        <v>121968</v>
+        <v>93139.2</v>
       </c>
       <c r="D5" t="n">
-        <v>106255.45</v>
+        <v>201332.74</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -12698,10 +13642,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>8960.280000000001</v>
+        <v>16072.04</v>
       </c>
       <c r="L5" t="n">
-        <v>14717.81</v>
+        <v>281232</v>
+      </c>
+      <c r="M5" t="n">
+        <v>17460</v>
       </c>
     </row>
     <row r="6">
@@ -12712,10 +13659,10 @@
         <v>55598.4</v>
       </c>
       <c r="C6" t="n">
-        <v>74844</v>
+        <v>57153.6</v>
       </c>
       <c r="D6" t="n">
-        <v>61032.68</v>
+        <v>115644.67</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -12724,7 +13671,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>27.75</v>
+        <v>81</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -12739,7 +13686,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12652</v>
+        <v>241758</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22320</v>
       </c>
     </row>
     <row r="7">
@@ -12762,7 +13712,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>83.25</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -12777,7 +13727,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>11699.64</v>
+        <v>223560</v>
+      </c>
+      <c r="M7" t="n">
+        <v>28350</v>
       </c>
     </row>
     <row r="8">
@@ -12815,7 +13768,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>11236.18</v>
+        <v>214704</v>
+      </c>
+      <c r="M8" t="n">
+        <v>16200</v>
       </c>
     </row>
     <row r="9">
@@ -12838,7 +13794,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12853,7 +13809,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>7096.09</v>
+        <v>135594</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -12891,7 +13850,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1257.57</v>
+        <v>24030</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -12931,6 +13893,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -12969,6 +13934,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13007,6 +13975,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13045,6 +14016,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -13083,6 +14057,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -13121,6 +14098,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -13159,6 +14139,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -13197,6 +14180,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -13235,6 +14221,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -13273,6 +14262,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13349,6 +14344,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -13387,6 +14385,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -13425,6 +14426,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13596,6 +14609,9 @@
       </c>
       <c r="L4" t="n">
         <v>300</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13635,6 +14651,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -13673,6 +14692,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14567,6 +15655,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -14605,6 +15696,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15499,6 +16659,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -15537,6 +16700,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -15575,6 +16741,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -15613,6 +16782,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -15651,6 +16823,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -15689,6 +16864,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -15727,6 +16905,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>13274563.5</v>
+        <v>13261109.4</v>
       </c>
       <c r="C5" t="n">
-        <v>44670780</v>
+        <v>34112232</v>
       </c>
       <c r="D5" t="n">
-        <v>38916058.06</v>
+        <v>73738114.56</v>
       </c>
       <c r="E5" t="n">
-        <v>5834352.03</v>
+        <v>10925159.85</v>
       </c>
       <c r="F5" t="n">
         <v>7500.06</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>182257.02</v>
+        <v>3755160</v>
       </c>
       <c r="I5" t="n">
-        <v>57499.5</v>
+        <v>64288.14</v>
       </c>
       <c r="J5" t="n">
-        <v>17499.9</v>
+        <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>474894.84</v>
+        <v>723241.62</v>
       </c>
       <c r="L5" t="n">
-        <v>167296.37</v>
+        <v>3196746</v>
+      </c>
+      <c r="M5" t="n">
+        <v>91980</v>
       </c>
     </row>
     <row r="6">
@@ -16440,22 +17675,22 @@
         <v>26059968</v>
       </c>
       <c r="C6" t="n">
-        <v>49671468</v>
+        <v>37930939.2</v>
       </c>
       <c r="D6" t="n">
-        <v>40505355.48</v>
+        <v>76749513.98</v>
       </c>
       <c r="E6" t="n">
-        <v>5492489.18</v>
+        <v>10285002</v>
       </c>
       <c r="F6" t="n">
         <v>20833.5</v>
       </c>
       <c r="G6" t="n">
-        <v>18537</v>
+        <v>54108</v>
       </c>
       <c r="H6" t="n">
-        <v>525109.36</v>
+        <v>10819170</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -16464,10 +17699,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>249607.8</v>
+        <v>418504.16</v>
       </c>
       <c r="L6" t="n">
-        <v>202536.59</v>
+        <v>3870126</v>
+      </c>
+      <c r="M6" t="n">
+        <v>137520</v>
       </c>
     </row>
     <row r="7">
@@ -16478,34 +17716,37 @@
         <v>23074791.3</v>
       </c>
       <c r="C7" t="n">
-        <v>28191240</v>
+        <v>21527856</v>
       </c>
       <c r="D7" t="n">
-        <v>26036035.81</v>
+        <v>49333059.07</v>
       </c>
       <c r="E7" t="n">
-        <v>2786255.99</v>
+        <v>5217424.65</v>
       </c>
       <c r="F7" t="n">
         <v>100000.8</v>
       </c>
       <c r="G7" t="n">
-        <v>34215.75</v>
+        <v>99873</v>
       </c>
       <c r="H7" t="n">
-        <v>24234.54</v>
+        <v>499320</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>122457.16</v>
+        <v>216851.1</v>
       </c>
       <c r="L7" t="n">
-        <v>191941.92</v>
+        <v>3667680</v>
+      </c>
+      <c r="M7" t="n">
+        <v>286650</v>
       </c>
     </row>
     <row r="8">
@@ -16516,22 +17757,22 @@
         <v>15013746</v>
       </c>
       <c r="C8" t="n">
-        <v>9979200</v>
+        <v>7620480</v>
       </c>
       <c r="D8" t="n">
-        <v>10631965.13</v>
+        <v>20145438.72</v>
       </c>
       <c r="E8" t="n">
-        <v>1138890.61</v>
+        <v>2132638.2</v>
       </c>
       <c r="F8" t="n">
         <v>118750.95</v>
       </c>
       <c r="G8" t="n">
-        <v>98845.5</v>
+        <v>288522</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -16540,10 +17781,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>57601.8</v>
+        <v>107211.65</v>
       </c>
       <c r="L8" t="n">
-        <v>96510.73</v>
+        <v>1844154</v>
+      </c>
+      <c r="M8" t="n">
+        <v>156600</v>
       </c>
     </row>
     <row r="9">
@@ -16554,22 +17798,22 @@
         <v>7875054</v>
       </c>
       <c r="C9" t="n">
-        <v>4213440</v>
+        <v>3217536</v>
       </c>
       <c r="D9" t="n">
-        <v>4897702.05</v>
+        <v>9280161.789999999</v>
       </c>
       <c r="E9" t="n">
-        <v>843389.92</v>
+        <v>1579296.15</v>
       </c>
       <c r="F9" t="n">
         <v>41667</v>
       </c>
       <c r="G9" t="n">
-        <v>35381.25</v>
+        <v>103275</v>
       </c>
       <c r="H9" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16578,10 +17822,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>128004</v>
+        <v>233942.81</v>
       </c>
       <c r="L9" t="n">
-        <v>29528.87</v>
+        <v>564246</v>
+      </c>
+      <c r="M9" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="10">
@@ -16592,22 +17839,22 @@
         <v>3980790</v>
       </c>
       <c r="C10" t="n">
-        <v>1247400</v>
+        <v>952560</v>
       </c>
       <c r="D10" t="n">
-        <v>1570959.52</v>
+        <v>2976652.8</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>90045</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>13320</v>
+        <v>38880</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16619,7 +17866,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>14587.81</v>
+        <v>278748</v>
+      </c>
+      <c r="M10" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="11">
@@ -16630,19 +17880,19 @@
         <v>2391840</v>
       </c>
       <c r="C11" t="n">
-        <v>942480</v>
+        <v>719712</v>
       </c>
       <c r="D11" t="n">
-        <v>1225829.95</v>
+        <v>2322701.57</v>
       </c>
       <c r="E11" t="n">
-        <v>67951.39999999999</v>
+        <v>127242.9</v>
       </c>
       <c r="F11" t="n">
         <v>41667</v>
       </c>
       <c r="G11" t="n">
-        <v>6105</v>
+        <v>17820</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -16657,7 +17907,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>13847.4</v>
+        <v>264600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -16668,22 +17921,22 @@
         <v>1830312</v>
       </c>
       <c r="C12" t="n">
-        <v>498960</v>
+        <v>381024</v>
       </c>
       <c r="D12" t="n">
-        <v>669553.78</v>
+        <v>1268669.95</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>41667</v>
       </c>
       <c r="G12" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H12" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16695,7 +17948,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3108.6</v>
+        <v>59400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -16706,10 +17962,10 @@
         <v>1853082</v>
       </c>
       <c r="C13" t="n">
-        <v>304920</v>
+        <v>232848</v>
       </c>
       <c r="D13" t="n">
-        <v>419103.11</v>
+        <v>794116.22</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16718,10 +17974,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H13" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -16733,7 +17989,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2260.8</v>
+        <v>43200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -16744,10 +18003,10 @@
         <v>1928322</v>
       </c>
       <c r="C14" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D14" t="n">
-        <v>273021.93</v>
+        <v>517321.73</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16756,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7770</v>
+        <v>22680</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -16771,7 +18030,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>97200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -16782,10 +18044,10 @@
         <v>825462</v>
       </c>
       <c r="C15" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D15" t="n">
-        <v>197824.53</v>
+        <v>374837.76</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16809,6 +18071,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16820,10 +18085,10 @@
         <v>309078</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16847,6 +18112,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16887,6 +18155,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -16925,6 +18196,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16963,6 +18237,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17001,6 +18278,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17039,6 +18319,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -17077,6 +18360,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -17115,6 +18401,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -17153,6 +18442,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1746.36</v>
+        <v>1743.03</v>
       </c>
       <c r="C4" t="n">
         <v>337680</v>
@@ -17320,10 +18621,13 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>21510</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9450</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3224.79</v>
+        <v>3221.28</v>
       </c>
       <c r="C5" t="n">
         <v>384552</v>
@@ -17358,10 +18662,13 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>27540</v>
+        <v>27570</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="6">
@@ -17384,7 +18691,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3750</v>
+        <v>3690</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -17396,10 +18703,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>15990</v>
+        <v>16020</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -17422,7 +18732,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1470</v>
+        <v>1530</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -17438,6 +18748,9 @@
       </c>
       <c r="L7" t="n">
         <v>6840</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -17477,6 +18790,9 @@
       <c r="L8" t="n">
         <v>2160</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -17515,6 +18831,9 @@
       <c r="L9" t="n">
         <v>720</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -17553,6 +18872,9 @@
       <c r="L10" t="n">
         <v>270</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -17591,6 +18913,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -17629,6 +18954,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1451.16</v>
+        <v>1449.58</v>
       </c>
       <c r="C5" t="n">
         <v>211503.6</v>
@@ -18290,10 +19666,13 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>11.34</v>
+        <v>6.29</v>
       </c>
       <c r="L5" t="n">
-        <v>5783.4</v>
+        <v>5789.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -18316,7 +19695,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>187.5</v>
+        <v>184.5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -18328,10 +19707,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>2.54</v>
       </c>
       <c r="L6" t="n">
-        <v>5916.3</v>
+        <v>5927.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -18354,7 +19736,7 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>220.5</v>
+        <v>229.5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -18366,10 +19748,13 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="L7" t="n">
         <v>4104</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -18404,10 +19789,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="L8" t="n">
         <v>1533.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -18442,10 +19830,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
         <v>583.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -18485,6 +19876,9 @@
       <c r="L10" t="n">
         <v>240.3</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -18523,6 +19917,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -18561,6 +19958,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -18599,6 +19999,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -18637,6 +20040,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18675,6 +20081,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3192542.1</v>
+        <v>3189067.2</v>
       </c>
       <c r="C5" t="n">
-        <v>11632698</v>
+        <v>8883151.199999999</v>
       </c>
       <c r="D5" t="n">
-        <v>10134113.41</v>
+        <v>19202109.7</v>
       </c>
       <c r="E5" t="n">
-        <v>1883818.99</v>
+        <v>3527559.45</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -19219,13 +20667,16 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>17499.9</v>
+        <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>241927.56</v>
+        <v>305368.68</v>
       </c>
       <c r="L5" t="n">
-        <v>54479.63</v>
+        <v>1042146</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10800</v>
       </c>
     </row>
     <row r="6">
@@ -19236,19 +20687,19 @@
         <v>6061492.8</v>
       </c>
       <c r="C6" t="n">
-        <v>12498948</v>
+        <v>9544651.199999999</v>
       </c>
       <c r="D6" t="n">
-        <v>10192457.61</v>
+        <v>19312660.22</v>
       </c>
       <c r="E6" t="n">
-        <v>1513236.82</v>
+        <v>2833623</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3468.75</v>
+        <v>9963</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -19260,10 +20711,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>83202.60000000001</v>
+        <v>123089.46</v>
       </c>
       <c r="L6" t="n">
-        <v>55731.55</v>
+        <v>1066932</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -19274,19 +20728,19 @@
         <v>3872414.7</v>
       </c>
       <c r="C7" t="n">
-        <v>5239080</v>
+        <v>4000752</v>
       </c>
       <c r="D7" t="n">
-        <v>4838555.33</v>
+        <v>9168090.619999999</v>
       </c>
       <c r="E7" t="n">
-        <v>881726.58</v>
+        <v>1651083.75</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>4079.25</v>
+        <v>12393</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -19295,13 +20749,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>69975.52</v>
+        <v>123914.91</v>
       </c>
       <c r="L7" t="n">
-        <v>38659.68</v>
+        <v>738720</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -19312,19 +20769,19 @@
         <v>1840608</v>
       </c>
       <c r="C8" t="n">
-        <v>1275120</v>
+        <v>973728</v>
       </c>
       <c r="D8" t="n">
-        <v>1358528.88</v>
+        <v>2574139.39</v>
       </c>
       <c r="E8" t="n">
-        <v>528770.64</v>
+        <v>990153.45</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1443</v>
+        <v>4212</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -19336,10 +20793,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>38401.2</v>
+        <v>71474.42999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>14446.51</v>
+        <v>276048</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -19350,19 +20810,19 @@
         <v>657162</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>740880</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>2136879.36</v>
       </c>
       <c r="E9" t="n">
-        <v>443889.43</v>
+        <v>831208.5</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2830.5</v>
+        <v>8262</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -19374,10 +20834,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>42668</v>
+        <v>77980.94</v>
       </c>
       <c r="L9" t="n">
-        <v>5493.74</v>
+        <v>104976</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -19388,10 +20851,10 @@
         <v>234234</v>
       </c>
       <c r="C10" t="n">
-        <v>360360</v>
+        <v>275184</v>
       </c>
       <c r="D10" t="n">
-        <v>453832.75</v>
+        <v>859921.92</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -19415,7 +20878,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2263.63</v>
+        <v>43254</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -19426,10 +20892,10 @@
         <v>114444</v>
       </c>
       <c r="C11" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D11" t="n">
-        <v>144215.29</v>
+        <v>273259.01</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -19453,7 +20919,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -19464,13 +20933,13 @@
         <v>77220</v>
       </c>
       <c r="C12" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D12" t="n">
-        <v>185987.16</v>
+        <v>352408.32</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -19491,6 +20960,9 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19502,10 +20974,10 @@
         <v>47916</v>
       </c>
       <c r="C13" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D13" t="n">
-        <v>114300.85</v>
+        <v>216577.15</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -19529,6 +21001,9 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19569,6 +21044,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -19607,6 +21085,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -19645,6 +21126,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -19683,6 +21167,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -19721,6 +21208,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -19759,6 +21249,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19797,6 +21290,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19835,6 +21331,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19873,6 +21372,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19911,6 +21413,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19949,6 +21454,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,7 +21621,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="H4" t="n">
         <v>210</v>
@@ -20120,6 +21637,9 @@
       </c>
       <c r="L4" t="n">
         <v>510</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20159,6 +21679,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -20197,6 +21720,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -20235,6 +21761,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -20273,6 +21802,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -20311,6 +21843,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21091,6 +22683,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -21129,6 +22724,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -21167,6 +22765,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -21205,6 +22806,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -21243,6 +22847,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22023,6 +23687,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -22061,6 +23728,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -22099,6 +23769,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -22137,6 +23810,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -22175,6 +23851,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -22213,6 +23892,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -22251,6 +23933,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -22289,6 +23974,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
@@ -549,7 +549,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>89370</v>
@@ -590,7 +590,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>84570</v>
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>58110</v>
@@ -672,7 +672,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>33960</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>14430</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>3870</v>
@@ -1553,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>34110</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>32130</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>20700</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>8460</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>930</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7.61</v>
+        <v>2.32</v>
       </c>
       <c r="L5" t="n">
         <v>6747.3</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.58</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>7659</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>5076</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>753.3</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>369656.83</v>
+        <v>112504.25</v>
       </c>
       <c r="L5" t="n">
         <v>1214514</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>270796.81</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
         <v>1378620</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92936.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>913680</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>116971.4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>135594</v>
@@ -10630,7 +10630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>7440</v>
@@ -11634,7 +11634,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>14.9</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
         <v>17759.7</v>
@@ -11675,7 +11675,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>8.619999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>21500.7</v>
@@ -11716,7 +11716,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>20376</v>
@@ -11757,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>10245.3</v>
@@ -11798,7 +11798,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.82</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
         <v>3134.7</v>
@@ -12638,7 +12638,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>1562.4</v>
@@ -13642,7 +13642,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>16072.04</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>281232</v>
@@ -17658,7 +17658,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>723241.62</v>
+        <v>176792.4</v>
       </c>
       <c r="L5" t="n">
         <v>3196746</v>
@@ -17699,7 +17699,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>418504.16</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
         <v>3870126</v>
@@ -17740,7 +17740,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>216851.1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3667680</v>
@@ -17781,7 +17781,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>107211.65</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1844154</v>
@@ -17822,7 +17822,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>233942.81</v>
+        <v>77980.94</v>
       </c>
       <c r="L9" t="n">
         <v>564246</v>
@@ -18621,7 +18621,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>21510</v>
@@ -18662,7 +18662,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>27570</v>
@@ -18703,7 +18703,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>16020</v>
@@ -18744,7 +18744,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>6840</v>
@@ -18785,7 +18785,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2160</v>
@@ -18826,7 +18826,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>720</v>
@@ -19666,7 +19666,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>6.29</v>
+        <v>1.32</v>
       </c>
       <c r="L5" t="n">
         <v>5789.7</v>
@@ -19707,7 +19707,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2.54</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>5927.4</v>
@@ -19748,7 +19748,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4104</v>
@@ -19789,7 +19789,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1533.6</v>
@@ -19830,7 +19830,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61</v>
+        <v>0.8</v>
       </c>
       <c r="L9" t="n">
         <v>583.2</v>
@@ -20670,7 +20670,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>305368.68</v>
+        <v>64288.14</v>
       </c>
       <c r="L5" t="n">
         <v>1042146</v>
@@ -20711,7 +20711,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>123089.46</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
         <v>1066932</v>
@@ -20752,7 +20752,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>123914.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>738720</v>
@@ -20793,7 +20793,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71474.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>276048</v>
@@ -20834,7 +20834,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>77980.94</v>
+        <v>38990.47</v>
       </c>
       <c r="L9" t="n">
         <v>104976</v>

--- a/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_2.3yrs_Future_Perfect.xlsx
@@ -560,7 +560,7 @@
         <v>31260</v>
       </c>
       <c r="H4" t="n">
-        <v>1470</v>
+        <v>2310</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -572,22 +572,22 @@
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>89370</v>
+        <v>90540</v>
       </c>
       <c r="M4" t="n">
-        <v>25830</v>
+        <v>34770</v>
       </c>
       <c r="N4" t="n">
-        <v>2610</v>
+        <v>4440</v>
       </c>
       <c r="O4" t="n">
-        <v>3570</v>
+        <v>3420</v>
       </c>
       <c r="P4" t="n">
-        <v>24630</v>
+        <v>14070</v>
       </c>
       <c r="Q4" t="n">
-        <v>11366.13</v>
+        <v>117786.06</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>27690</v>
       </c>
       <c r="H5" t="n">
-        <v>1830</v>
+        <v>1740</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -625,22 +625,22 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>84570</v>
+        <v>100380</v>
       </c>
       <c r="M5" t="n">
-        <v>15330</v>
+        <v>34530</v>
       </c>
       <c r="N5" t="n">
-        <v>1410</v>
+        <v>1530</v>
       </c>
       <c r="O5" t="n">
-        <v>1560</v>
+        <v>2370</v>
       </c>
       <c r="P5" t="n">
-        <v>35010</v>
+        <v>27960</v>
       </c>
       <c r="Q5" t="n">
-        <v>16609.87</v>
+        <v>172126.52</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>20040</v>
       </c>
       <c r="H6" t="n">
-        <v>3330</v>
+        <v>3900</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>58110</v>
+        <v>76560</v>
       </c>
       <c r="M6" t="n">
-        <v>5730</v>
+        <v>21180</v>
       </c>
       <c r="N6" t="n">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="O6" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="P6" t="n">
-        <v>26550</v>
+        <v>29490</v>
       </c>
       <c r="Q6" t="n">
-        <v>18360.43</v>
+        <v>190267.38</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>12330</v>
       </c>
       <c r="H7" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -731,10 +731,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>33960</v>
+        <v>57750</v>
       </c>
       <c r="M7" t="n">
-        <v>2730</v>
+        <v>17160</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -743,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>24390</v>
+        <v>34200</v>
       </c>
       <c r="Q7" t="n">
-        <v>13690.31</v>
+        <v>141871.32</v>
       </c>
     </row>
     <row r="8">
@@ -784,10 +784,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>14430</v>
+        <v>30810</v>
       </c>
       <c r="M8" t="n">
-        <v>870</v>
+        <v>6600</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -796,10 +796,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>12990</v>
+        <v>23160</v>
       </c>
       <c r="Q8" t="n">
-        <v>8462.290000000001</v>
+        <v>87693.92999999999</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>2250</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>3870</v>
+        <v>19110</v>
       </c>
       <c r="M9" t="n">
-        <v>360</v>
+        <v>4140</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>11880</v>
+        <v>23910</v>
       </c>
       <c r="Q9" t="n">
-        <v>4438.67</v>
+        <v>45997.47</v>
       </c>
     </row>
     <row r="10">
@@ -890,10 +890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1740</v>
+        <v>4200</v>
       </c>
       <c r="M10" t="n">
-        <v>90</v>
+        <v>2220</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -902,10 +902,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3420</v>
+        <v>4980</v>
       </c>
       <c r="Q10" t="n">
-        <v>2243.72</v>
+        <v>23251.43</v>
       </c>
     </row>
     <row r="11">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1470</v>
+        <v>2700</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5040</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3750</v>
+        <v>8850</v>
       </c>
       <c r="Q11" t="n">
-        <v>1348.13</v>
+        <v>13970.52</v>
       </c>
     </row>
     <row r="12">
@@ -996,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>330</v>
+        <v>1650</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>540</v>
+        <v>1500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1031.63</v>
+        <v>10690.69</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>150</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>240</v>
+        <v>540</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1064,7 +1064,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1044.46</v>
+        <v>10823.68</v>
       </c>
     </row>
     <row r="14">
@@ -1102,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>1410</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1086.87</v>
+        <v>11263.15</v>
       </c>
     </row>
     <row r="15">
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>465.26</v>
+        <v>4821.45</v>
       </c>
     </row>
     <row r="16">
@@ -1208,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>174.21</v>
+        <v>1805.3</v>
       </c>
     </row>
     <row r="17">
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>36.83</v>
+        <v>381.64</v>
       </c>
     </row>
     <row r="18">
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.68</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="19">
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.22</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="20">
@@ -1852,7 +1852,7 @@
         <v>16500</v>
       </c>
       <c r="H4" t="n">
-        <v>1260</v>
+        <v>2010</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,13 +1864,13 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>34110</v>
+        <v>40740</v>
       </c>
       <c r="M4" t="n">
-        <v>6900</v>
+        <v>9120</v>
       </c>
       <c r="N4" t="n">
-        <v>30</v>
+        <v>570</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>900.96</v>
+        <v>102109.14</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>12720</v>
       </c>
       <c r="H5" t="n">
-        <v>1830</v>
+        <v>1620</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1917,13 +1917,13 @@
         <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>32130</v>
+        <v>39150</v>
       </c>
       <c r="M5" t="n">
-        <v>8580</v>
+        <v>13290</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1054.75</v>
+        <v>119538.9</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>6600</v>
       </c>
       <c r="H6" t="n">
-        <v>3330</v>
+        <v>3900</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,10 +1970,10 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>20700</v>
+        <v>27900</v>
       </c>
       <c r="M6" t="n">
-        <v>3420</v>
+        <v>7680</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1201.1</v>
+        <v>136124.1</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>3600</v>
       </c>
       <c r="H7" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8460</v>
+        <v>14040</v>
       </c>
       <c r="M7" t="n">
-        <v>2010</v>
+        <v>3870</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1059.97</v>
+        <v>120129.48</v>
       </c>
     </row>
     <row r="8">
@@ -2076,10 +2076,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2790</v>
+        <v>5520</v>
       </c>
       <c r="M8" t="n">
-        <v>660</v>
+        <v>1920</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>675.05</v>
+        <v>76506.12</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>870</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>930</v>
+        <v>2340</v>
       </c>
       <c r="M9" t="n">
-        <v>150</v>
+        <v>1080</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>288.68</v>
+        <v>32717.52</v>
       </c>
     </row>
     <row r="10">
@@ -2182,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>660</v>
+        <v>1080</v>
       </c>
       <c r="M10" t="n">
-        <v>60</v>
+        <v>750</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>130.95</v>
+        <v>14841</v>
       </c>
     </row>
     <row r="11">
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1170</v>
+        <v>2370</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1770</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>87.8</v>
+        <v>9951.120000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>1290</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>72.73999999999999</v>
+        <v>8243.639999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,11 +2341,11 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>420</v>
+      </c>
+      <c r="M13" t="n">
         <v>90</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>85.45</v>
+        <v>9684.9</v>
       </c>
     </row>
     <row r="14">
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>95.8</v>
+        <v>10856.88</v>
       </c>
     </row>
     <row r="15">
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.04</v>
+        <v>4311.54</v>
       </c>
     </row>
     <row r="16">
@@ -2500,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>29</v>
+        <v>3286.44</v>
       </c>
     </row>
     <row r="17">
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.43</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="18">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>658.8</v>
+        <v>583.2</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -3209,13 +3209,13 @@
         <v>2.32</v>
       </c>
       <c r="L5" t="n">
-        <v>6747.3</v>
+        <v>8221.5</v>
       </c>
       <c r="M5" t="n">
-        <v>171.6</v>
+        <v>265.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>52.74</v>
+        <v>5976.94</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>330</v>
       </c>
       <c r="H6" t="n">
-        <v>1898.1</v>
+        <v>2223</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,10 +3262,10 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>7659</v>
+        <v>10323</v>
       </c>
       <c r="M6" t="n">
-        <v>273.6</v>
+        <v>614.4</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>900.8200000000001</v>
+        <v>102093.08</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>540</v>
       </c>
       <c r="H7" t="n">
-        <v>87.59999999999999</v>
+        <v>284.7</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,10 +3315,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5076</v>
+        <v>8424</v>
       </c>
       <c r="M7" t="n">
-        <v>703.5</v>
+        <v>1354.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>847.97</v>
+        <v>96103.58</v>
       </c>
     </row>
     <row r="8">
@@ -3368,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1980.9</v>
+        <v>3919.2</v>
       </c>
       <c r="M8" t="n">
-        <v>363</v>
+        <v>1056</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>641.3</v>
+        <v>72680.81</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>739.5</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,10 +3421,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>753.3</v>
+        <v>1895.4</v>
       </c>
       <c r="M9" t="n">
-        <v>105</v>
+        <v>756</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>280.02</v>
+        <v>31735.99</v>
       </c>
     </row>
     <row r="10">
@@ -3474,10 +3474,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>587.4</v>
+        <v>961.2</v>
       </c>
       <c r="M10" t="n">
-        <v>51</v>
+        <v>637.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>130.95</v>
+        <v>14841</v>
       </c>
     </row>
     <row r="11">
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1170</v>
+        <v>2370</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1593</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>87.8</v>
+        <v>9951.120000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>1290</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>627</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>72.73999999999999</v>
+        <v>8243.639999999999</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,11 +3633,11 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>420</v>
+      </c>
+      <c r="M13" t="n">
         <v>90</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>85.45999999999999</v>
+        <v>9684.9</v>
       </c>
     </row>
     <row r="14">
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>95.8</v>
+        <v>10856.88</v>
       </c>
     </row>
     <row r="15">
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.04</v>
+        <v>4311.54</v>
       </c>
     </row>
     <row r="16">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>29</v>
+        <v>3286.44</v>
       </c>
     </row>
     <row r="17">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.43</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="18">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3755160</v>
+        <v>3324240</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -4501,13 +4501,13 @@
         <v>112504.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1214514</v>
+        <v>1479870</v>
       </c>
       <c r="M5" t="n">
-        <v>60060</v>
+        <v>93030</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>31642.65</v>
+        <v>3586167</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>17820</v>
       </c>
       <c r="H6" t="n">
-        <v>10819170</v>
+        <v>12671100</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,10 +4554,10 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>1378620</v>
+        <v>1858140</v>
       </c>
       <c r="M6" t="n">
-        <v>95760</v>
+        <v>215040</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>540492.75</v>
+        <v>61255845</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>29160</v>
       </c>
       <c r="H7" t="n">
-        <v>499320</v>
+        <v>1622790</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,10 +4607,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>913680</v>
+        <v>1516320</v>
       </c>
       <c r="M7" t="n">
-        <v>246225</v>
+        <v>474075</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>508783.68</v>
+        <v>57662150.4</v>
       </c>
     </row>
     <row r="8">
@@ -4660,10 +4660,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>356562</v>
+        <v>705456</v>
       </c>
       <c r="M8" t="n">
-        <v>127050</v>
+        <v>369600</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>384780.78</v>
+        <v>43608488.4</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>39933</v>
       </c>
       <c r="H9" t="n">
-        <v>342000</v>
+        <v>1026000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>135594</v>
+        <v>341172</v>
       </c>
       <c r="M9" t="n">
-        <v>36750</v>
+        <v>264600</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>168014.09</v>
+        <v>19041596.64</v>
       </c>
     </row>
     <row r="10">
@@ -4766,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>105732</v>
+        <v>173016</v>
       </c>
       <c r="M10" t="n">
-        <v>17850</v>
+        <v>223125</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>78570</v>
+        <v>8904600</v>
       </c>
     </row>
     <row r="11">
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210600</v>
+        <v>426600</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>557550</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>52682.4</v>
+        <v>5970672</v>
       </c>
     </row>
     <row r="12">
@@ -4872,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>43200</v>
+        <v>232200</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>219450</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>43642.8</v>
+        <v>4946184</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>16200</v>
+        <v>75600</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>51273</v>
+        <v>5810940</v>
       </c>
     </row>
     <row r="14">
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>140400</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>57477.6</v>
+        <v>6514128</v>
       </c>
     </row>
     <row r="15">
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>172800</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>22825.8</v>
+        <v>2586924</v>
       </c>
     </row>
     <row r="16">
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>64800</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17398.8</v>
+        <v>1971864</v>
       </c>
     </row>
     <row r="17">
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>259.2</v>
+        <v>29376</v>
       </c>
     </row>
     <row r="18">
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>307.8</v>
+        <v>34884</v>
       </c>
     </row>
     <row r="19">
@@ -5752,10 +5752,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.46</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="5">
@@ -9625,13 +9625,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>270</v>
+        <v>570</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>79.41</v>
+        <v>430.92</v>
       </c>
     </row>
     <row r="5">
@@ -13492,19 +13492,19 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>22350</v>
+        <v>15390</v>
       </c>
       <c r="M4" t="n">
-        <v>5880</v>
+        <v>5280</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P4" t="n">
-        <v>3330</v>
+        <v>5850</v>
       </c>
       <c r="Q4" t="n">
         <v>1511.51</v>
@@ -13545,10 +13545,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7440</v>
+        <v>11280</v>
       </c>
       <c r="M5" t="n">
-        <v>2910</v>
+        <v>10260</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -13557,7 +13557,7 @@
         <v>30</v>
       </c>
       <c r="P5" t="n">
-        <v>5400</v>
+        <v>960</v>
       </c>
       <c r="Q5" t="n">
         <v>323.53</v>
@@ -13598,10 +13598,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3630</v>
+        <v>10830</v>
       </c>
       <c r="M6" t="n">
-        <v>930</v>
+        <v>8250</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -13610,7 +13610,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6900</v>
+        <v>870</v>
       </c>
       <c r="Q6" t="n">
         <v>39.17</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2070</v>
+        <v>14940</v>
       </c>
       <c r="M7" t="n">
-        <v>270</v>
+        <v>7620</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -13663,7 +13663,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5700</v>
+        <v>7830</v>
       </c>
       <c r="Q7" t="n">
         <v>15.96</v>
@@ -13704,10 +13704,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1680</v>
+        <v>12420</v>
       </c>
       <c r="M8" t="n">
-        <v>90</v>
+        <v>3210</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -13716,7 +13716,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5460</v>
+        <v>9360</v>
       </c>
       <c r="Q8" t="n">
         <v>21.2</v>
@@ -13757,19 +13757,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>930</v>
+        <v>13380</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1590</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P9" t="n">
-        <v>5130</v>
+        <v>12600</v>
       </c>
       <c r="Q9" t="n">
         <v>14.06</v>
@@ -13810,7 +13810,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>150</v>
+        <v>1800</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -13822,7 +13822,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>630</v>
+        <v>1800</v>
       </c>
       <c r="Q10" t="n">
         <v>1.56</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>658.8</v>
+        <v>626.4</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -14837,22 +14837,22 @@
         <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>17759.7</v>
+        <v>21079.8</v>
       </c>
       <c r="M5" t="n">
-        <v>306.6</v>
+        <v>690.6</v>
       </c>
       <c r="N5" t="n">
-        <v>14.1</v>
+        <v>15.3</v>
       </c>
       <c r="O5" t="n">
-        <v>78</v>
+        <v>118.5</v>
       </c>
       <c r="P5" t="n">
-        <v>700.2</v>
+        <v>559.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>830.49</v>
+        <v>8606.33</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>1002</v>
       </c>
       <c r="H6" t="n">
-        <v>1898.1</v>
+        <v>2223</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -14890,22 +14890,22 @@
         <v>1.01</v>
       </c>
       <c r="L6" t="n">
-        <v>21500.7</v>
+        <v>28327.2</v>
       </c>
       <c r="M6" t="n">
-        <v>458.4</v>
+        <v>1694.4</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>22.5</v>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>82.5</v>
       </c>
       <c r="P6" t="n">
-        <v>3982.5</v>
+        <v>4423.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>13770.32</v>
+        <v>142700.53</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>1849.5</v>
       </c>
       <c r="H7" t="n">
-        <v>87.59999999999999</v>
+        <v>284.7</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -14943,10 +14943,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>20376</v>
+        <v>34650</v>
       </c>
       <c r="M7" t="n">
-        <v>955.5</v>
+        <v>6006</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -14955,10 +14955,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6097.5</v>
+        <v>8550</v>
       </c>
       <c r="Q7" t="n">
-        <v>10952.25</v>
+        <v>113497.06</v>
       </c>
     </row>
     <row r="8">
@@ -14996,10 +14996,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>10245.3</v>
+        <v>21875.1</v>
       </c>
       <c r="M8" t="n">
-        <v>478.5</v>
+        <v>3630</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -15008,10 +15008,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4936.2</v>
+        <v>8800.799999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>8039.18</v>
+        <v>83309.23</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>1912.5</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>1.61</v>
       </c>
       <c r="L9" t="n">
-        <v>3134.7</v>
+        <v>15479.1</v>
       </c>
       <c r="M9" t="n">
-        <v>252</v>
+        <v>2898</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="P9" t="n">
-        <v>5940</v>
+        <v>11955</v>
       </c>
       <c r="Q9" t="n">
-        <v>4305.51</v>
+        <v>44617.55</v>
       </c>
     </row>
     <row r="10">
@@ -15102,10 +15102,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1548.6</v>
+        <v>3738</v>
       </c>
       <c r="M10" t="n">
-        <v>76.5</v>
+        <v>1887</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -15114,10 +15114,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2907</v>
+        <v>4233</v>
       </c>
       <c r="Q10" t="n">
-        <v>2243.72</v>
+        <v>23251.43</v>
       </c>
     </row>
     <row r="11">
@@ -15155,10 +15155,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1470</v>
+        <v>2700</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -15167,10 +15167,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3375</v>
+        <v>7965</v>
       </c>
       <c r="Q11" t="n">
-        <v>1348.13</v>
+        <v>13970.52</v>
       </c>
     </row>
     <row r="12">
@@ -15208,10 +15208,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>330</v>
+        <v>1650</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>883.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -15220,10 +15220,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>540</v>
+        <v>1500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1031.63</v>
+        <v>10690.69</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>150</v>
       </c>
       <c r="H13" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,10 +15261,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>240</v>
+        <v>540</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1044.46</v>
+        <v>10823.68</v>
       </c>
     </row>
     <row r="14">
@@ -15314,10 +15314,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>1410</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -15329,7 +15329,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1086.87</v>
+        <v>11263.15</v>
       </c>
     </row>
     <row r="15">
@@ -15367,10 +15367,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -15382,7 +15382,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>465.26</v>
+        <v>4821.45</v>
       </c>
     </row>
     <row r="16">
@@ -15420,7 +15420,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -15435,7 +15435,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>174.21</v>
+        <v>1805.3</v>
       </c>
     </row>
     <row r="17">
@@ -15473,7 +15473,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -15488,7 +15488,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>36.83</v>
+        <v>381.64</v>
       </c>
     </row>
     <row r="18">
@@ -15526,7 +15526,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -15541,7 +15541,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.68</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="19">
@@ -15594,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.22</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="20">
@@ -16129,10 +16129,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1562.4</v>
+        <v>2368.8</v>
       </c>
       <c r="M5" t="n">
-        <v>58.2</v>
+        <v>205.2</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -16141,7 +16141,7 @@
         <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>108</v>
+        <v>19.2</v>
       </c>
       <c r="Q5" t="n">
         <v>16.18</v>
@@ -16182,10 +16182,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1343.1</v>
+        <v>4007.1</v>
       </c>
       <c r="M6" t="n">
-        <v>74.40000000000001</v>
+        <v>660</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -16194,7 +16194,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1035</v>
+        <v>130.5</v>
       </c>
       <c r="Q6" t="n">
         <v>29.38</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1242</v>
+        <v>8964</v>
       </c>
       <c r="M7" t="n">
-        <v>94.5</v>
+        <v>2667</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -16247,7 +16247,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1425</v>
+        <v>1957.5</v>
       </c>
       <c r="Q7" t="n">
         <v>12.77</v>
@@ -16288,10 +16288,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1192.8</v>
+        <v>8818.200000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>49.5</v>
+        <v>1765.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -16300,7 +16300,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2074.8</v>
+        <v>3556.8</v>
       </c>
       <c r="Q8" t="n">
         <v>20.14</v>
@@ -16341,19 +16341,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>753.3</v>
+        <v>10837.8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1113</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2565</v>
+        <v>6300</v>
       </c>
       <c r="Q9" t="n">
         <v>13.64</v>
@@ -16394,7 +16394,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>133.5</v>
+        <v>1602</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>535.5</v>
+        <v>1530</v>
       </c>
       <c r="Q10" t="n">
         <v>1.56</v>
@@ -17421,10 +17421,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>281232</v>
+        <v>426384</v>
       </c>
       <c r="M5" t="n">
-        <v>20370</v>
+        <v>71820</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -17433,7 +17433,7 @@
         <v>255</v>
       </c>
       <c r="P5" t="n">
-        <v>7020</v>
+        <v>1248</v>
       </c>
       <c r="Q5" t="n">
         <v>9705.85</v>
@@ -17474,10 +17474,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>241758</v>
+        <v>721278</v>
       </c>
       <c r="M6" t="n">
-        <v>26040</v>
+        <v>231000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -17486,7 +17486,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>67275</v>
+        <v>8482.5</v>
       </c>
       <c r="Q6" t="n">
         <v>17627.22</v>
@@ -17527,10 +17527,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>223560</v>
+        <v>1613520</v>
       </c>
       <c r="M7" t="n">
-        <v>33075</v>
+        <v>933450</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -17539,7 +17539,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>92625</v>
+        <v>127237.5</v>
       </c>
       <c r="Q7" t="n">
         <v>7660.22</v>
@@ -17580,10 +17580,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>214704</v>
+        <v>1587276</v>
       </c>
       <c r="M8" t="n">
-        <v>17325</v>
+        <v>617925</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -17592,7 +17592,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>134862</v>
+        <v>231192</v>
       </c>
       <c r="Q8" t="n">
         <v>12086.28</v>
@@ -17633,19 +17633,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>135594</v>
+        <v>1950804</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>389550</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2805</v>
       </c>
       <c r="P9" t="n">
-        <v>166725</v>
+        <v>409500</v>
       </c>
       <c r="Q9" t="n">
         <v>8183.85</v>
@@ -17686,7 +17686,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>24030</v>
+        <v>288360</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -17698,7 +17698,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>34807.5</v>
+        <v>99450</v>
       </c>
       <c r="Q10" t="n">
         <v>937.4400000000001</v>
@@ -18660,7 +18660,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>300</v>
+        <v>630</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -18669,13 +18669,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P4" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.49</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="5">
@@ -18728,7 +18728,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="6">
@@ -20020,7 +20020,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="6">
@@ -21312,7 +21312,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.59</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="6">
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3755160</v>
+        <v>3570480</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -22589,22 +22589,22 @@
         <v>176792.4</v>
       </c>
       <c r="L5" t="n">
-        <v>3196746</v>
+        <v>3794364</v>
       </c>
       <c r="M5" t="n">
-        <v>107310</v>
+        <v>241710</v>
       </c>
       <c r="N5" t="n">
-        <v>2397</v>
+        <v>2601</v>
       </c>
       <c r="O5" t="n">
-        <v>13260</v>
+        <v>20145</v>
       </c>
       <c r="P5" t="n">
-        <v>45513</v>
+        <v>36348</v>
       </c>
       <c r="Q5" t="n">
-        <v>498296.23</v>
+        <v>5163795.63</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>54108</v>
       </c>
       <c r="H6" t="n">
-        <v>10819170</v>
+        <v>12671100</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -22642,22 +22642,22 @@
         <v>49235.78</v>
       </c>
       <c r="L6" t="n">
-        <v>3870126</v>
+        <v>5098896</v>
       </c>
       <c r="M6" t="n">
-        <v>160440</v>
+        <v>593040</v>
       </c>
       <c r="N6" t="n">
-        <v>1530</v>
+        <v>3825</v>
       </c>
       <c r="O6" t="n">
-        <v>2550</v>
+        <v>14025</v>
       </c>
       <c r="P6" t="n">
-        <v>258862.5</v>
+        <v>287527.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>8262194.4</v>
+        <v>85620321</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>99873</v>
       </c>
       <c r="H7" t="n">
-        <v>499320</v>
+        <v>1622790</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22695,10 +22695,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3667680</v>
+        <v>6237000</v>
       </c>
       <c r="M7" t="n">
-        <v>334425</v>
+        <v>2102100</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -22707,10 +22707,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>396337.5</v>
+        <v>555750</v>
       </c>
       <c r="Q7" t="n">
-        <v>6571347.26</v>
+        <v>68098235.76000001</v>
       </c>
     </row>
     <row r="8">
@@ -22748,10 +22748,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1844154</v>
+        <v>3937518</v>
       </c>
       <c r="M8" t="n">
-        <v>167475</v>
+        <v>1270500</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -22760,10 +22760,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>320853</v>
+        <v>572052</v>
       </c>
       <c r="Q8" t="n">
-        <v>4823507.12</v>
+        <v>49985537.54</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>103275</v>
       </c>
       <c r="H9" t="n">
-        <v>342000</v>
+        <v>1026000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>77980.94</v>
       </c>
       <c r="L9" t="n">
-        <v>564246</v>
+        <v>2786238</v>
       </c>
       <c r="M9" t="n">
-        <v>88200</v>
+        <v>1014300</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2805</v>
       </c>
       <c r="P9" t="n">
-        <v>386100</v>
+        <v>777075</v>
       </c>
       <c r="Q9" t="n">
-        <v>2583304.08</v>
+        <v>26770530.16</v>
       </c>
     </row>
     <row r="10">
@@ -22854,10 +22854,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>278748</v>
+        <v>672840</v>
       </c>
       <c r="M10" t="n">
-        <v>26775</v>
+        <v>660450</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -22866,10 +22866,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>188955</v>
+        <v>275145</v>
       </c>
       <c r="Q10" t="n">
-        <v>1346230.8</v>
+        <v>13950859.5</v>
       </c>
     </row>
     <row r="11">
@@ -22907,10 +22907,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>264600</v>
+        <v>486000</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1587600</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -22919,10 +22919,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>219375</v>
+        <v>517725</v>
       </c>
       <c r="Q11" t="n">
-        <v>808876.8</v>
+        <v>8382312</v>
       </c>
     </row>
     <row r="12">
@@ -22960,10 +22960,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>59400</v>
+        <v>297000</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>309225</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -22972,10 +22972,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>35100</v>
+        <v>97500</v>
       </c>
       <c r="Q12" t="n">
-        <v>618978.24</v>
+        <v>6414411.6</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>8100</v>
       </c>
       <c r="H13" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,10 +23013,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>43200</v>
+        <v>97200</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23028,7 +23028,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>626678.64</v>
+        <v>6494210.1</v>
       </c>
     </row>
     <row r="14">
@@ -23066,10 +23066,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>97200</v>
+        <v>253800</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -23081,7 +23081,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>652123.4399999999</v>
+        <v>6757892.1</v>
       </c>
     </row>
     <row r="15">
@@ -23119,10 +23119,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>172800</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>279156.24</v>
+        <v>2892869.1</v>
       </c>
     </row>
     <row r="16">
@@ -23172,7 +23172,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>64800</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23187,7 +23187,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>104524.56</v>
+        <v>1083177.9</v>
       </c>
     </row>
     <row r="17">
@@ -23225,7 +23225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -23240,7 +23240,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>22096.8</v>
+        <v>228987</v>
       </c>
     </row>
     <row r="18">
@@ -23278,7 +23278,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -23293,7 +23293,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2209.68</v>
+        <v>22898.7</v>
       </c>
     </row>
     <row r="19">
@@ -23346,7 +23346,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>133.92</v>
+        <v>1387.8</v>
       </c>
     </row>
     <row r="20">
@@ -23828,22 +23828,22 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>21510</v>
+        <v>24420</v>
       </c>
       <c r="M4" t="n">
-        <v>9450</v>
+        <v>15510</v>
       </c>
       <c r="N4" t="n">
-        <v>2550</v>
+        <v>3480</v>
       </c>
       <c r="O4" t="n">
-        <v>2490</v>
+        <v>1530</v>
       </c>
       <c r="P4" t="n">
-        <v>3690</v>
+        <v>4770</v>
       </c>
       <c r="Q4" t="n">
-        <v>1777.89</v>
+        <v>17430.3</v>
       </c>
     </row>
     <row r="5">
@@ -23881,22 +23881,22 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>27570</v>
+        <v>33030</v>
       </c>
       <c r="M5" t="n">
-        <v>1800</v>
+        <v>4230</v>
       </c>
       <c r="N5" t="n">
-        <v>1410</v>
+        <v>1500</v>
       </c>
       <c r="O5" t="n">
-        <v>1530</v>
+        <v>2340</v>
       </c>
       <c r="P5" t="n">
-        <v>4020</v>
+        <v>5100</v>
       </c>
       <c r="Q5" t="n">
-        <v>3285.71</v>
+        <v>32212.8</v>
       </c>
     </row>
     <row r="6">
@@ -23934,22 +23934,22 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>16020</v>
+        <v>18660</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="N6" t="n">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="O6" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="P6" t="n">
-        <v>2250</v>
+        <v>3240</v>
       </c>
       <c r="Q6" t="n">
-        <v>3512.91</v>
+        <v>34440.3</v>
       </c>
     </row>
     <row r="7">
@@ -23987,7 +23987,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6840</v>
+        <v>8250</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -23999,10 +23999,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4440</v>
+        <v>4920</v>
       </c>
       <c r="Q7" t="n">
-        <v>1889.89</v>
+        <v>18528.3</v>
       </c>
     </row>
     <row r="8">
@@ -24040,7 +24040,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2160</v>
+        <v>2640</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -24052,10 +24052,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1290</v>
+        <v>3150</v>
       </c>
       <c r="Q8" t="n">
-        <v>853.37</v>
+        <v>8366.4</v>
       </c>
     </row>
     <row r="9">
@@ -24093,7 +24093,7 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>720</v>
+        <v>960</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -24108,7 +24108,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>304.68</v>
+        <v>2987.1</v>
       </c>
     </row>
     <row r="10">
@@ -24146,7 +24146,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>108.6</v>
+        <v>1064.7</v>
       </c>
     </row>
     <row r="11">
@@ -24199,7 +24199,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -24214,7 +24214,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>53.06</v>
+        <v>520.2</v>
       </c>
     </row>
     <row r="12">
@@ -24252,7 +24252,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -24267,7 +24267,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>35.8</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13">
@@ -24320,7 +24320,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.22</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="14">
@@ -24373,7 +24373,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.5</v>
+        <v>230.4</v>
       </c>
     </row>
     <row r="15">
@@ -25173,22 +25173,22 @@
         <v>1.32</v>
       </c>
       <c r="L5" t="n">
-        <v>5789.7</v>
+        <v>6936.3</v>
       </c>
       <c r="M5" t="n">
-        <v>36</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>14.1</v>
+        <v>15</v>
       </c>
       <c r="O5" t="n">
-        <v>76.5</v>
+        <v>117</v>
       </c>
       <c r="P5" t="n">
-        <v>80.40000000000001</v>
+        <v>102</v>
       </c>
       <c r="Q5" t="n">
-        <v>164.29</v>
+        <v>1610.64</v>
       </c>
     </row>
     <row r="6">
@@ -25226,22 +25226,22 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>5927.4</v>
+        <v>6904.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>22.5</v>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>82.5</v>
       </c>
       <c r="P6" t="n">
-        <v>337.5</v>
+        <v>486</v>
       </c>
       <c r="Q6" t="n">
-        <v>2634.68</v>
+        <v>25830.22</v>
       </c>
     </row>
     <row r="7">
@@ -25279,7 +25279,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4104</v>
+        <v>4950</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -25291,10 +25291,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1110</v>
+        <v>1230</v>
       </c>
       <c r="Q7" t="n">
-        <v>1511.91</v>
+        <v>14822.64</v>
       </c>
     </row>
     <row r="8">
@@ -25332,7 +25332,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1533.6</v>
+        <v>1874.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -25344,10 +25344,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>490.2</v>
+        <v>1197</v>
       </c>
       <c r="Q8" t="n">
-        <v>810.7</v>
+        <v>7948.08</v>
       </c>
     </row>
     <row r="9">
@@ -25385,7 +25385,7 @@
         <v>0.8</v>
       </c>
       <c r="L9" t="n">
-        <v>583.2</v>
+        <v>777.6</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -25400,7 +25400,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>295.54</v>
+        <v>2897.49</v>
       </c>
     </row>
     <row r="10">
@@ -25438,7 +25438,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>240.3</v>
+        <v>267</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -25453,7 +25453,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>108.6</v>
+        <v>1064.7</v>
       </c>
     </row>
     <row r="11">
@@ -25491,7 +25491,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -25506,7 +25506,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>53.06</v>
+        <v>520.2</v>
       </c>
     </row>
     <row r="12">
@@ -25544,7 +25544,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -25559,7 +25559,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>35.8</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13">
@@ -25612,7 +25612,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.22</v>
+        <v>217.8</v>
       </c>
     </row>
     <row r="14">
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.5</v>
+        <v>230.4</v>
       </c>
     </row>
     <row r="15">
@@ -26465,22 +26465,22 @@
         <v>64288.14</v>
       </c>
       <c r="L5" t="n">
-        <v>1042146</v>
+        <v>1248534</v>
       </c>
       <c r="M5" t="n">
-        <v>12600</v>
+        <v>29610</v>
       </c>
       <c r="N5" t="n">
-        <v>2397</v>
+        <v>2550</v>
       </c>
       <c r="O5" t="n">
-        <v>13005</v>
+        <v>19890</v>
       </c>
       <c r="P5" t="n">
-        <v>5226</v>
+        <v>6630</v>
       </c>
       <c r="Q5" t="n">
-        <v>98571.17</v>
+        <v>966384</v>
       </c>
     </row>
     <row r="6">
@@ -26518,22 +26518,22 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>1066932</v>
+        <v>1242756</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>9240</v>
       </c>
       <c r="N6" t="n">
-        <v>1530</v>
+        <v>3825</v>
       </c>
       <c r="O6" t="n">
-        <v>2550</v>
+        <v>14025</v>
       </c>
       <c r="P6" t="n">
-        <v>21937.5</v>
+        <v>31590</v>
       </c>
       <c r="Q6" t="n">
-        <v>1580809.77</v>
+        <v>15498135</v>
       </c>
     </row>
     <row r="7">
@@ -26571,7 +26571,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>738720</v>
+        <v>891000</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -26583,10 +26583,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>72150</v>
+        <v>79950</v>
       </c>
       <c r="Q7" t="n">
-        <v>907145.5699999999</v>
+        <v>8893584</v>
       </c>
     </row>
     <row r="8">
@@ -26624,7 +26624,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>276048</v>
+        <v>337392</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -26636,10 +26636,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>31863</v>
+        <v>77805</v>
       </c>
       <c r="Q8" t="n">
-        <v>486422.5</v>
+        <v>4768848</v>
       </c>
     </row>
     <row r="9">
@@ -26677,7 +26677,7 @@
         <v>38990.47</v>
       </c>
       <c r="L9" t="n">
-        <v>104976</v>
+        <v>139968</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -26692,7 +26692,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>177326.2</v>
+        <v>1738492.2</v>
       </c>
     </row>
     <row r="10">
@@ -26730,7 +26730,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>43254</v>
+        <v>48060</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -26745,7 +26745,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>65159.64</v>
+        <v>638820</v>
       </c>
     </row>
     <row r="11">
@@ -26783,7 +26783,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>32400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -26798,7 +26798,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>31836.24</v>
+        <v>312120</v>
       </c>
     </row>
     <row r="12">
@@ -26836,7 +26836,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -26851,7 +26851,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>21481.2</v>
+        <v>210600</v>
       </c>
     </row>
     <row r="13">
@@ -26904,7 +26904,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13329.36</v>
+        <v>130680</v>
       </c>
     </row>
     <row r="14">
@@ -26957,7 +26957,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>14100.48</v>
+        <v>138240</v>
       </c>
     </row>
     <row r="15">
@@ -27692,7 +27692,7 @@
         <v>540</v>
       </c>
       <c r="H4" t="n">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -27704,7 +27704,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>510</v>
+        <v>1440</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.71</v>
+        <v>218.79</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>18.9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>61560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3402</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
